--- a/VT_REG1_IND_V12.xlsx
+++ b/VT_REG1_IND_V12.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VEDA_Release\Demo_S012_Vonline\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\veda-test_model\Demo_S012_Vonline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A381A909-FDDF-4D42-8E05-2A1A7069295A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C6E5F6-C57A-477E-88E8-2695EF82BF92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="901" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6540" yWindow="2505" windowWidth="21600" windowHeight="11295" tabRatio="901" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -27,7 +27,20 @@
   <definedNames>
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -3803,6 +3816,9 @@
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="EnergyBalance"/>
       <sheetName val="EB1"/>
